--- a/docagent_clean_mvp/sample_data/raw_excels/VSA_SetA.xlsx
+++ b/docagent_clean_mvp/sample_data/raw_excels/VSA_SetA.xlsx
@@ -2004,7 +2004,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Subcontractors and fourth parties handling customer data are subject to the same security due-diligence review as direct vendors.</t>
+          <t>Standard Third-Party Risk control mandates that subcontractors and fourth parties handling customer data are subject to the same security due-diligence review as direct vendors. [VSA-052]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Compliant - subcontractor register up to date</t>
+          <t>Compliant - evidence on file</t>
         </is>
       </c>
     </row>
